--- a/pipeline/lz_spec/landing_zone_spec.xlsx
+++ b/pipeline/lz_spec/landing_zone_spec.xlsx
@@ -76,7 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
